--- a/countrydataset.xlsx
+++ b/countrydataset.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94891f26e3ff8bc0/Desktop/SeniorCapstone/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="158" documentId="8_{A693E8EE-547A-4705-ADE5-9AD41FB95419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C033C26-F664-4029-8FAA-812EBE792171}"/>
+  <xr:revisionPtr revIDLastSave="219" documentId="8_{A693E8EE-547A-4705-ADE5-9AD41FB95419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CF3AD2E-BFE0-4A6F-BD84-37C913E3D506}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E5978300-F4D3-4197-8D1D-15CC19E49CE3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="73">
   <si>
     <t>Indoor</t>
   </si>
@@ -243,6 +243,18 @@
   </si>
   <si>
     <t>Vizcaya Museum and Gardens</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Afternoon</t>
+  </si>
+  <si>
+    <t>Morning</t>
+  </si>
+  <si>
+    <t>Evening</t>
   </si>
 </sst>
 </file>
@@ -614,10 +626,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6B3BB34-F5B7-4402-8DBD-B2AD4CFA5C2D}">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>54</v>
       </c>
@@ -627,8 +639,11 @@
       <c r="C1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -638,8 +653,11 @@
       <c r="C2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>57</v>
       </c>
@@ -649,8 +667,11 @@
       <c r="C3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>57</v>
       </c>
@@ -660,8 +681,11 @@
       <c r="C4" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>57</v>
       </c>
@@ -671,8 +695,11 @@
       <c r="C5" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -682,8 +709,11 @@
       <c r="C6" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>57</v>
       </c>
@@ -693,8 +723,11 @@
       <c r="C7" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>57</v>
       </c>
@@ -704,8 +737,11 @@
       <c r="C8" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>57</v>
       </c>
@@ -715,8 +751,11 @@
       <c r="C9" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>57</v>
       </c>
@@ -726,8 +765,11 @@
       <c r="C10" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -737,8 +779,11 @@
       <c r="C11" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -748,8 +793,11 @@
       <c r="C12" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>57</v>
       </c>
@@ -759,8 +807,11 @@
       <c r="C13" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>57</v>
       </c>
@@ -770,8 +821,11 @@
       <c r="C14" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>57</v>
       </c>
@@ -781,8 +835,11 @@
       <c r="C15" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>57</v>
       </c>
@@ -792,8 +849,11 @@
       <c r="C16" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>57</v>
       </c>
@@ -803,8 +863,11 @@
       <c r="C17" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>57</v>
       </c>
@@ -814,8 +877,11 @@
       <c r="C18" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>57</v>
       </c>
@@ -825,8 +891,11 @@
       <c r="C19" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>57</v>
       </c>
@@ -836,8 +905,11 @@
       <c r="C20" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>57</v>
       </c>
@@ -847,8 +919,11 @@
       <c r="C21" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>63</v>
       </c>
@@ -858,8 +933,11 @@
       <c r="C22" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>63</v>
       </c>
@@ -869,8 +947,11 @@
       <c r="C23" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>63</v>
       </c>
@@ -880,8 +961,11 @@
       <c r="C24" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -891,8 +975,11 @@
       <c r="C25" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D25" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -902,8 +989,11 @@
       <c r="C26" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D26" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -913,8 +1003,11 @@
       <c r="C27" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D27" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -924,8 +1017,11 @@
       <c r="C28" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D28" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -935,8 +1031,11 @@
       <c r="C29" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D29" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -946,8 +1045,11 @@
       <c r="C30" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D30" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -957,8 +1059,11 @@
       <c r="C31" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>63</v>
       </c>
@@ -968,8 +1073,11 @@
       <c r="C32" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D32" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>63</v>
       </c>
@@ -979,8 +1087,11 @@
       <c r="C33" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D33" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>63</v>
       </c>
@@ -990,8 +1101,11 @@
       <c r="C34" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D34" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>63</v>
       </c>
@@ -1001,8 +1115,11 @@
       <c r="C35" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D35" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>63</v>
       </c>
@@ -1012,8 +1129,11 @@
       <c r="C36" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D36" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1023,8 +1143,11 @@
       <c r="C37" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D37" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>63</v>
       </c>
@@ -1034,8 +1157,11 @@
       <c r="C38" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D38" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>63</v>
       </c>
@@ -1045,8 +1171,11 @@
       <c r="C39" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D39" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>63</v>
       </c>
@@ -1056,8 +1185,11 @@
       <c r="C40" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D40" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>63</v>
       </c>
@@ -1067,8 +1199,11 @@
       <c r="C41" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D41" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>64</v>
       </c>
@@ -1078,8 +1213,11 @@
       <c r="C42" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D42" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>64</v>
       </c>
@@ -1089,8 +1227,11 @@
       <c r="C43" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>64</v>
       </c>
@@ -1100,8 +1241,11 @@
       <c r="C44" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D44" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>64</v>
       </c>
@@ -1111,8 +1255,11 @@
       <c r="C45" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D45" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>64</v>
       </c>
@@ -1122,8 +1269,11 @@
       <c r="C46" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D46" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>64</v>
       </c>
@@ -1133,8 +1283,11 @@
       <c r="C47" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D47" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>64</v>
       </c>
@@ -1144,8 +1297,11 @@
       <c r="C48" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D48" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>64</v>
       </c>
@@ -1155,8 +1311,11 @@
       <c r="C49" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D49" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>64</v>
       </c>
@@ -1166,8 +1325,11 @@
       <c r="C50" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D50" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>64</v>
       </c>
@@ -1177,8 +1339,11 @@
       <c r="C51" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D51" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>64</v>
       </c>
@@ -1188,8 +1353,11 @@
       <c r="C52" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D52" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>64</v>
       </c>
@@ -1199,8 +1367,11 @@
       <c r="C53" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D53" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>64</v>
       </c>
@@ -1210,8 +1381,11 @@
       <c r="C54" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D54" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>64</v>
       </c>
@@ -1221,8 +1395,11 @@
       <c r="C55" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D55" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>64</v>
       </c>
@@ -1232,8 +1409,11 @@
       <c r="C56" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D56" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -1243,8 +1423,11 @@
       <c r="C57" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D57" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>64</v>
       </c>
@@ -1254,8 +1437,11 @@
       <c r="C58" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D58" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -1265,8 +1451,11 @@
       <c r="C59" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D59" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>64</v>
       </c>
@@ -1276,8 +1465,11 @@
       <c r="C60" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D60" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>64</v>
       </c>
@@ -1286,6 +1478,9 @@
       </c>
       <c r="C61" t="s">
         <v>1</v>
+      </c>
+      <c r="D61" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
